--- a/scripts/Provincial_Tools/tbl_spp.xlsx
+++ b/scripts/Provincial_Tools/tbl_spp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\T\git\p3t_ArcGIS_Pro_Tools\scripts\Provincial_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5765D7-E02F-4458-9173-922659E9D489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADDB876-06C3-4259-BE30-46B7381064E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="instruction" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="uniq_only" sheetId="2" r:id="rId3"/>
     <sheet name="tbl_sql_classify" sheetId="5" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="808">
   <si>
     <t>spc</t>
   </si>
@@ -2485,13 +2485,16 @@
   </si>
   <si>
     <t>originally PT but in Larry's script this gets merged with PO. We will leave it as PT</t>
+  </si>
+  <si>
+    <t>Rob K - should be grouped with MR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2641,12 +2644,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="34">
@@ -3038,7 +3035,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="42" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3511,52 +3508,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2F87D7-D9FE-4D3B-BF72-BDA824B4466E}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="93.1171875" customWidth="1"/>
+    <col min="1" max="1" width="93.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>802</v>
       </c>
@@ -3574,17 +3571,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G122"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.41015625" customWidth="1"/>
-    <col min="3" max="3" width="13.5859375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="34.1171875" customWidth="1"/>
-    <col min="5" max="5" width="12.5859375" customWidth="1"/>
-    <col min="6" max="6" width="10.29296875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3607,7 +3604,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3628,7 +3625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>168</v>
       </c>
@@ -3649,7 +3646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3670,7 +3667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -3691,7 +3688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -3712,7 +3709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>173</v>
       </c>
@@ -3733,7 +3730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3754,7 +3751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3775,7 +3772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3796,7 +3793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>172</v>
       </c>
@@ -3817,7 +3814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3838,7 +3835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -3859,7 +3856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>184</v>
       </c>
@@ -3880,7 +3877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>187</v>
       </c>
@@ -3901,7 +3898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>178</v>
       </c>
@@ -3922,7 +3919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -3943,7 +3940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>181</v>
       </c>
@@ -3964,7 +3961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -3985,7 +3982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -4006,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>189</v>
       </c>
@@ -4027,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>190</v>
       </c>
@@ -4048,7 +4045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -4069,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -4090,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -4111,7 +4108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -4132,7 +4129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -4153,7 +4150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>72</v>
       </c>
@@ -4174,7 +4171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -4195,7 +4192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -4216,7 +4213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>204</v>
       </c>
@@ -4237,7 +4234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>205</v>
       </c>
@@ -4258,7 +4255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>239</v>
       </c>
@@ -4279,7 +4276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>208</v>
       </c>
@@ -4300,7 +4297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>209</v>
       </c>
@@ -4320,8 +4317,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G35" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>210</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>211</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>215</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>93</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>216</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>104</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>227</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>228</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>229</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>231</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>232</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>169</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>170</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>171</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>174</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>175</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>177</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>179</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>180</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>183</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>185</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>186</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>188</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>191</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>192</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>56</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>193</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>194</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>195</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>196</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>197</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>198</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>199</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>200</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>202</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>203</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>206</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>207</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>212</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>213</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>214</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>222</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>230</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>236</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>238</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>240</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>241</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>242</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>217</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>218</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>220</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>221</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>106</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>118</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>128</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>224</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>225</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>123</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>226</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>133</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>136</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>138</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>140</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>98</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>219</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>99</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>147</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>234</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>237</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>144</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>145</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>176</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -6182,152 +6182,152 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>147</v>
       </c>
@@ -6340,12 +6340,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3A972D-6C57-4F42-AAB0-282B41C0517C}">
   <dimension ref="A1:F481"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="92.1171875" customWidth="1"/>
+    <col min="6" max="6" width="92.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>249</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -7085,7 +7085,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -7165,7 +7165,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -7725,7 +7725,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -7765,7 +7765,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -8285,7 +8285,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -8465,7 +8465,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -8645,7 +8645,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -8805,7 +8805,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -8845,7 +8845,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -8885,7 +8885,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -9025,7 +9025,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -9205,7 +9205,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>300</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>301</v>
       </c>
@@ -9245,7 +9245,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>302</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>303</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>304</v>
       </c>
@@ -9305,7 +9305,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>310</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>311</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>312</v>
       </c>
@@ -9365,7 +9365,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>313</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>315</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>316</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>317</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>318</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>319</v>
       </c>
@@ -9485,7 +9485,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>320</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>321</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>322</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>323</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>324</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>325</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>326</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>327</v>
       </c>
@@ -9645,7 +9645,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>350</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
         <v>351</v>
       </c>
@@ -9685,7 +9685,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>352</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>353</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>354</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>355</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>356</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>357</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>358</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>359</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>360</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>361</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>362</v>
       </c>
@@ -9905,7 +9905,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>363</v>
       </c>
@@ -9925,7 +9925,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>364</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>365</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>366</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>367</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>368</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>369</v>
       </c>
@@ -10045,7 +10045,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>370</v>
       </c>
@@ -10065,7 +10065,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>371</v>
       </c>
@@ -10085,7 +10085,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>372</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>400</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>401</v>
       </c>
@@ -10145,7 +10145,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>402</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>403</v>
       </c>
@@ -10185,7 +10185,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>404</v>
       </c>
@@ -10205,7 +10205,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>405</v>
       </c>
@@ -10225,7 +10225,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>406</v>
       </c>
@@ -10245,7 +10245,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>407</v>
       </c>
@@ -10265,7 +10265,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>408</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>409</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>410</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>411</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>412</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>413</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>414</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>415</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>416</v>
       </c>
@@ -10445,7 +10445,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>417</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>418</v>
       </c>
@@ -10485,7 +10485,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>419</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>420</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>421</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>422</v>
       </c>
@@ -10565,7 +10565,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>423</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>424</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>425</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>426</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>427</v>
       </c>
@@ -10665,7 +10665,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>428</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>429</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>430</v>
       </c>
@@ -10725,7 +10725,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>431</v>
       </c>
@@ -10745,7 +10745,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>432</v>
       </c>
@@ -10765,7 +10765,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>433</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>434</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>435</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>436</v>
       </c>
@@ -10845,7 +10845,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>437</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>438</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>439</v>
       </c>
@@ -10905,7 +10905,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>440</v>
       </c>
@@ -10925,7 +10925,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>441</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>442</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>443</v>
       </c>
@@ -10985,7 +10985,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>444</v>
       </c>
@@ -11005,7 +11005,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>445</v>
       </c>
@@ -11025,7 +11025,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>446</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>447</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>448</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>449</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>450</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>451</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>452</v>
       </c>
@@ -11165,7 +11165,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>453</v>
       </c>
@@ -11185,7 +11185,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>454</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>455</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>456</v>
       </c>
@@ -11245,7 +11245,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>457</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>458</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>459</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>460</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>461</v>
       </c>
@@ -11345,7 +11345,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>462</v>
       </c>
@@ -11365,7 +11365,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>463</v>
       </c>
@@ -11385,7 +11385,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
         <v>464</v>
       </c>
@@ -11405,7 +11405,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>465</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
         <v>466</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>467</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>468</v>
       </c>
@@ -11485,7 +11485,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>469</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>470</v>
       </c>
@@ -11525,7 +11525,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>471</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
         <v>472</v>
       </c>
@@ -11565,7 +11565,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>473</v>
       </c>
@@ -11585,7 +11585,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
         <v>474</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>480</v>
       </c>
@@ -11625,7 +11625,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>481</v>
       </c>
@@ -11645,7 +11645,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>482</v>
       </c>
@@ -11665,7 +11665,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>483</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>484</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
         <v>485</v>
       </c>
@@ -11725,7 +11725,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>486</v>
       </c>
@@ -11745,7 +11745,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
         <v>487</v>
       </c>
@@ -11765,7 +11765,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
         <v>488</v>
       </c>
@@ -11785,7 +11785,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
         <v>490</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
         <v>491</v>
       </c>
@@ -11825,7 +11825,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="3">
         <v>492</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
         <v>493</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="3">
         <v>494</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
         <v>495</v>
       </c>
@@ -11905,7 +11905,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
         <v>496</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
         <v>497</v>
       </c>
@@ -11945,7 +11945,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
         <v>600</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
         <v>601</v>
       </c>
@@ -11985,7 +11985,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="3">
         <v>602</v>
       </c>
@@ -12005,7 +12005,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
         <v>603</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="3">
         <v>604</v>
       </c>
@@ -12045,7 +12045,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
         <v>610</v>
       </c>
@@ -12065,7 +12065,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="3">
         <v>611</v>
       </c>
@@ -12085,7 +12085,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
         <v>612</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="3">
         <v>613</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
         <v>614</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="3">
         <v>615</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
         <v>616</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="3">
         <v>617</v>
       </c>
@@ -12205,7 +12205,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
         <v>618</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="3">
         <v>619</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
         <v>620</v>
       </c>
@@ -12265,7 +12265,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="3">
         <v>621</v>
       </c>
@@ -12285,7 +12285,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
         <v>622</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="3">
         <v>623</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
         <v>624</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="3">
         <v>625</v>
       </c>
@@ -12365,7 +12365,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="3">
         <v>626</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="3">
         <v>627</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="3">
         <v>628</v>
       </c>
@@ -12425,7 +12425,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="3">
         <v>629</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
         <v>630</v>
       </c>
@@ -12465,7 +12465,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="3">
         <v>631</v>
       </c>
@@ -12485,7 +12485,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="3">
         <v>632</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="3">
         <v>633</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
         <v>634</v>
       </c>
@@ -12545,7 +12545,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="3">
         <v>635</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
         <v>636</v>
       </c>
@@ -12585,7 +12585,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="3">
         <v>640</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
         <v>641</v>
       </c>
@@ -12625,7 +12625,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="3">
         <v>642</v>
       </c>
@@ -12645,7 +12645,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
         <v>643</v>
       </c>
@@ -12665,7 +12665,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
         <v>644</v>
       </c>
@@ -12685,7 +12685,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
         <v>645</v>
       </c>
@@ -12705,7 +12705,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="3">
         <v>646</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
         <v>647</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="3">
         <v>650</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>651</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
         <v>652</v>
       </c>
@@ -12805,7 +12805,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
         <v>653</v>
       </c>
@@ -12825,7 +12825,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="3">
         <v>654</v>
       </c>
@@ -12845,7 +12845,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
         <v>655</v>
       </c>
@@ -12865,7 +12865,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
         <v>656</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
         <v>657</v>
       </c>
@@ -12905,7 +12905,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="3">
         <v>658</v>
       </c>
@@ -12925,7 +12925,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
         <v>659</v>
       </c>
@@ -12945,7 +12945,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="3">
         <v>660</v>
       </c>
@@ -12965,7 +12965,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
         <v>661</v>
       </c>
@@ -12985,7 +12985,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="3">
         <v>662</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
         <v>663</v>
       </c>
@@ -13025,7 +13025,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="3">
         <v>664</v>
       </c>
@@ -13045,7 +13045,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="3">
         <v>665</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="3">
         <v>666</v>
       </c>
@@ -13085,7 +13085,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="3">
         <v>667</v>
       </c>
@@ -13105,7 +13105,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="3">
         <v>668</v>
       </c>
@@ -13125,7 +13125,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
         <v>669</v>
       </c>
@@ -13145,7 +13145,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="3">
         <v>670</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
         <v>671</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="3">
         <v>672</v>
       </c>
@@ -13205,7 +13205,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
         <v>673</v>
       </c>
@@ -13225,7 +13225,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="3">
         <v>674</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
         <v>675</v>
       </c>
@@ -13265,7 +13265,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
         <v>676</v>
       </c>
@@ -13285,7 +13285,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
         <v>680</v>
       </c>
@@ -13305,7 +13305,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="3">
         <v>681</v>
       </c>
@@ -13325,7 +13325,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
         <v>682</v>
       </c>
@@ -13345,7 +13345,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
         <v>683</v>
       </c>
@@ -13365,7 +13365,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
         <v>684</v>
       </c>
@@ -13385,7 +13385,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="3">
         <v>685</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
         <v>686</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="3">
         <v>687</v>
       </c>
@@ -13445,7 +13445,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
         <v>688</v>
       </c>
@@ -13465,7 +13465,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
         <v>689</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
         <v>690</v>
       </c>
@@ -13505,7 +13505,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="3">
         <v>691</v>
       </c>
@@ -13525,7 +13525,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
         <v>692</v>
       </c>
@@ -13545,7 +13545,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
         <v>693</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
         <v>694</v>
       </c>
@@ -13585,7 +13585,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="3">
         <v>695</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
         <v>696</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="3">
         <v>697</v>
       </c>
@@ -13645,7 +13645,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="3">
         <v>698</v>
       </c>
@@ -13665,7 +13665,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="3">
         <v>699</v>
       </c>
@@ -13685,7 +13685,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
         <v>700</v>
       </c>
@@ -13705,7 +13705,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
         <v>701</v>
       </c>
@@ -13725,7 +13725,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
         <v>702</v>
       </c>
@@ -13745,7 +13745,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="3">
         <v>703</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
         <v>704</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="3">
         <v>705</v>
       </c>
@@ -13805,7 +13805,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
         <v>706</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="3">
         <v>707</v>
       </c>
@@ -13845,7 +13845,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
         <v>708</v>
       </c>
@@ -13865,7 +13865,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="3">
         <v>709</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
         <v>710</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="3">
         <v>711</v>
       </c>
@@ -13925,7 +13925,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
         <v>712</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="3">
         <v>713</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
         <v>714</v>
       </c>
@@ -13985,7 +13985,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="3">
         <v>715</v>
       </c>
@@ -14005,7 +14005,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
         <v>716</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="3">
         <v>717</v>
       </c>
@@ -14045,7 +14045,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
         <v>718</v>
       </c>
@@ -14065,7 +14065,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="3">
         <v>719</v>
       </c>
@@ -14085,7 +14085,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="3">
         <v>720</v>
       </c>
@@ -14105,7 +14105,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="3">
         <v>721</v>
       </c>
@@ -14125,7 +14125,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="3">
         <v>722</v>
       </c>
@@ -14145,7 +14145,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="3">
         <v>723</v>
       </c>
@@ -14165,7 +14165,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="3">
         <v>724</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="3">
         <v>725</v>
       </c>
@@ -14205,7 +14205,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="3">
         <v>726</v>
       </c>
@@ -14225,7 +14225,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="3">
         <v>727</v>
       </c>
@@ -14245,7 +14245,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="3">
         <v>728</v>
       </c>
@@ -14265,7 +14265,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="3">
         <v>729</v>
       </c>
@@ -14285,7 +14285,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="3">
         <v>730</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="3">
         <v>731</v>
       </c>
@@ -14325,7 +14325,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="3">
         <v>732</v>
       </c>
@@ -14345,7 +14345,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="3">
         <v>733</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="3">
         <v>734</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="3">
         <v>735</v>
       </c>
@@ -14405,7 +14405,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="3">
         <v>736</v>
       </c>
@@ -14425,7 +14425,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="3">
         <v>737</v>
       </c>
@@ -14445,7 +14445,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="3">
         <v>738</v>
       </c>
@@ -14465,7 +14465,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="3">
         <v>739</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="3">
         <v>740</v>
       </c>
@@ -14505,7 +14505,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="3">
         <v>741</v>
       </c>
@@ -14525,7 +14525,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="3">
         <v>742</v>
       </c>
@@ -14545,7 +14545,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="3">
         <v>743</v>
       </c>
@@ -14565,7 +14565,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="3">
         <v>744</v>
       </c>
@@ -14585,7 +14585,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="3">
         <v>745</v>
       </c>
@@ -14605,7 +14605,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="3">
         <v>746</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="3">
         <v>747</v>
       </c>
@@ -14645,7 +14645,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="3">
         <v>748</v>
       </c>
@@ -14665,7 +14665,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="3">
         <v>749</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="3">
         <v>750</v>
       </c>
@@ -14705,7 +14705,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="3">
         <v>751</v>
       </c>
@@ -14725,7 +14725,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="3">
         <v>752</v>
       </c>
@@ -14745,7 +14745,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="3">
         <v>753</v>
       </c>
@@ -14765,7 +14765,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="3">
         <v>754</v>
       </c>
@@ -14785,7 +14785,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="3">
         <v>755</v>
       </c>
@@ -14805,7 +14805,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="3">
         <v>756</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="3">
         <v>757</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="3">
         <v>758</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="3">
         <v>759</v>
       </c>
@@ -14885,7 +14885,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="3">
         <v>760</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="3">
         <v>761</v>
       </c>
@@ -14925,7 +14925,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="3">
         <v>762</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="3">
         <v>763</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="3">
         <v>764</v>
       </c>
@@ -14985,7 +14985,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="3">
         <v>765</v>
       </c>
@@ -15005,7 +15005,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="3">
         <v>766</v>
       </c>
@@ -15025,7 +15025,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="3">
         <v>767</v>
       </c>
@@ -15045,7 +15045,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="3">
         <v>768</v>
       </c>
@@ -15065,7 +15065,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="3">
         <v>769</v>
       </c>
@@ -15085,7 +15085,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="3">
         <v>770</v>
       </c>
@@ -15105,7 +15105,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="3">
         <v>771</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="3">
         <v>772</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="3">
         <v>773</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="3">
         <v>774</v>
       </c>
@@ -15185,7 +15185,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="3">
         <v>775</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="3">
         <v>776</v>
       </c>
@@ -15225,7 +15225,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="3">
         <v>777</v>
       </c>
@@ -15245,7 +15245,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="3">
         <v>778</v>
       </c>
@@ -15265,7 +15265,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="3">
         <v>779</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="3">
         <v>780</v>
       </c>
@@ -15305,7 +15305,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="3">
         <v>781</v>
       </c>
@@ -15325,7 +15325,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="3">
         <v>782</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="3">
         <v>783</v>
       </c>
@@ -15365,7 +15365,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="3">
         <v>784</v>
       </c>
@@ -15385,7 +15385,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="3">
         <v>785</v>
       </c>
@@ -15405,7 +15405,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="3">
         <v>786</v>
       </c>
@@ -15425,7 +15425,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="3">
         <v>787</v>
       </c>
@@ -15445,7 +15445,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="3">
         <v>788</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="3">
         <v>789</v>
       </c>
@@ -15485,7 +15485,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="3">
         <v>790</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="3">
         <v>791</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="3">
         <v>792</v>
       </c>
@@ -15545,7 +15545,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="3">
         <v>793</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="3">
         <v>794</v>
       </c>
@@ -15585,7 +15585,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="3">
         <v>795</v>
       </c>
@@ -15605,7 +15605,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="3">
         <v>796</v>
       </c>
@@ -15625,7 +15625,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="3">
         <v>797</v>
       </c>
@@ -15645,7 +15645,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="3">
         <v>798</v>
       </c>
@@ -15665,7 +15665,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="3">
         <v>799</v>
       </c>
@@ -15685,7 +15685,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="3">
         <v>800</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="3">
         <v>801</v>
       </c>
@@ -15725,7 +15725,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="3">
         <v>802</v>
       </c>
@@ -15745,7 +15745,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="3">
         <v>803</v>
       </c>
@@ -15765,7 +15765,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="3">
         <v>804</v>
       </c>
@@ -15785,7 +15785,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="3">
         <v>805</v>
       </c>
@@ -15805,7 +15805,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="3">
         <v>810</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="3">
         <v>811</v>
       </c>
@@ -15845,7 +15845,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="3">
         <v>812</v>
       </c>
@@ -15865,7 +15865,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="3">
         <v>813</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="3">
         <v>814</v>
       </c>
@@ -15905,7 +15905,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="3">
         <v>815</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="3">
         <v>816</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="3">
         <v>817</v>
       </c>
